--- a/stories/arbres/ATOM-SEC.MAI.001-04.xlsx
+++ b/stories/arbres/ATOM-SEC.MAI.001-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Dahlia joue dans la salle de jeux. Ses voitures en bois sont par terre. Papa range des livres près de la porte. La pièce est un peu sombre. Dahlia veut plus de lumière. Elle regarde ses mains. Les mains restent avec les jouets. Dahlia appelle un adulte. Elle dit : papa, la lumière. Papa vient. Papa allume. La pièce devient claire. Maman entre. Maman dit : on va appeler un adulte. Les prises sont pour les adultes. Les mains restent avec les jouets. Dahlia reprend une voiture rouge. Elle la fait rouler tout doux. Parce qu'elle a appelé, la lumière est là. Les mains tiennent les jouets. Dahlia est calme. Papa s'assoit près d'elle. Ils font un petit garage. Les mains restent avec les jouets.</t>
+          <t>Dahlia joue dans la salle de jeux. Ses voitures en bois sont par terre. Papa range des livres près de la porte. La pièce est un peu sombre. Dahlia veut plus de lumière. Elle regarde ses mains. Les mains restent avec les jouets. Dahlia appelle un adulte. Papa, la lumière. Papa vient. Papa allume. La pièce devient claire. Maman entre. On va appeler un adulte. Les prises sont pour les adultes. Les mains restent avec les jouets. Dahlia reprend une voiture rouge. Elle la fait rouler tout doux. Parce qu'elle a appelé, la lumière est là. Les mains tiennent les jouets. Dahlia est calme. Papa s'assoit près d'elle. Ils font un petit garage. Les mains restent avec les jouets.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Dahlia joue dans la salle de jeux. Ses voitures en bois sont par terre. Papa range des livres près de la porte. La pièce est un peu sombre. Dahlia veut plus de lumière. Elle regarde ses mains. Les mains restent avec les jouets. Dahlia appelle un adulte.
+narrateur|Papa, la lumière. Papa vient. Papa allume.
+narrateur|La pièce devient claire. Maman entre.
+maman|On va appeler un adulte.
+narrateur|Les prises sont pour les adultes. Les mains restent avec les jouets. Dahlia reprend une voiture rouge. Elle la fait rouler tout doux. Parce qu'elle a appelé, la lumière est là. Les mains tiennent les jouets. Dahlia est calme. Papa s'assoit près d'elle. Ils font un petit garage. Les mains restent avec les jouets.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1494,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Dahlia veut la lumière. Que fait-elle ?</t>
         </is>
       </c>
     </row>
@@ -1641,6 +1671,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Dahlia a appelé un adulte. Les mains étaient avec les jouets. Papa et maman sont là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1803,6 +1838,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Dahlia pose la voiture dans le garage. La lumière reste allumée.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1965,6 +2005,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1983,7 +2028,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2000,6 +2045,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.MAI.001-04.xlsx
+++ b/stories/arbres/ATOM-SEC.MAI.001-04.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,11 @@
 narrateur|Les prises sont pour les adultes. Les mains restent avec les jouets. Dahlia reprend une voiture rouge. Elle la fait rouler tout doux. Parce qu'elle a appelé, la lumière est là. Les mains tiennent les jouets. Dahlia est calme. Papa s'assoit près d'elle. Ils font un petit garage. Les mains restent avec les jouets.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc,voiture_passe</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1501,6 +1511,7 @@
           <t>narrateur|Dahlia veut la lumière. Que fait-elle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1676,6 +1687,7 @@
           <t>narrateur|Dahlia a appelé un adulte. Les mains étaient avec les jouets. Papa et maman sont là.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1843,6 +1855,7 @@
           <t>narrateur|Dahlia pose la voiture dans le garage. La lumière reste allumée.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2010,6 +2023,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2028,7 +2042,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2052,6 +2066,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2066,7 +2094,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2253,6 +2281,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SEC.MAI.001-04.xlsx
+++ b/stories/arbres/ATOM-SEC.MAI.001-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Dahlia appelle pour la lumière</t>
+          <t>Les voitures dans le rayon</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>La poussière danse dans un rayon. Les voitures de bois dorment. La pièce est un peu sombre. Nino va appeler un adulte. Les mains avec les jouets.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Dahlia joue dans la salle de jeux. Ses voitures en bois sont par terre. Papa range des livres près de la porte. La pièce est un peu sombre. Dahlia veut plus de lumière. Elle regarde ses mains. Les mains restent avec les jouets. Dahlia appelle un adulte. Papa, la lumière. Papa vient. Papa allume. La pièce devient claire. Maman entre. On va appeler un adulte. Les prises sont pour les adultes. Les mains restent avec les jouets. Dahlia reprend une voiture rouge. Elle la fait rouler tout doux. Parce qu'elle a appelé, la lumière est là. Les mains tiennent les jouets. Dahlia est calme. Papa s'assoit près d'elle. Ils font un petit garage. Les mains restent avec les jouets.</t>
+          <t>La poussière danse dans un rayon. Le rayon est mince, tout pâle. Des voitures en bois dorment par terre. Le bois est lisse, un peu froid. Une pile de livres attend près de la porte. Papa range un livre, tout doux. La pièce est un peu sombre. Nino vit ici, avec papa et maman. Papa, la poussière danse ! Oui. C'est le soleil. Tu vois tes voitures ? Oui. Elles dorment. En ce moment, Nino prend une voiture rouge. Il la fait rouler tout doux. Le bois fait un petit bruit. Le rayon pâle ne suffit plus. Papa, la lumière. Nino regarde ses mains. Les mains avec les jouets. Nino appelle papa. On va appeler un adulte. J'arrive, Nino. Papa vient. Papa allume. La pièce devient claire. Les voitures de bois brillent. Tu as appelé un adulte ? Oui, maman. Bravo, Nino. On appelle papa ou maman pour la lumière. Les prises sont pour les adultes. Les mains avec les jouets. Nino reprend la voiture rouge. Il fait un petit garage. Deux livres forment les murs. Le garage ! Oui. Tu as fait du bon travail. Parce qu'il a appelé, la lumière est là. Les mains tiennent les jouets. Tu ranges une voiture dans le garage ? Oui. Papa s'assoit près de lui. Le plancher est un peu froid. Tes mains sont avec les jouets ? Oui, maman. Bravo. La poussière ne se voit plus. La pièce est claire, tout simple. J'ai appelé un adulte. Oui. C'est bien. Nino est calme. La voiture rouge entre dans le garage. Elle fait un petit toc. Les autres voitures attendent leur tour.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,16 +1324,69 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Dahlia joue dans la salle de jeux. Ses voitures en bois sont par terre. Papa range des livres près de la porte. La pièce est un peu sombre. Dahlia veut plus de lumière. Elle regarde ses mains. Les mains restent avec les jouets. Dahlia appelle un adulte.
-narrateur|Papa, la lumière. Papa vient. Papa allume.
-narrateur|La pièce devient claire. Maman entre.
-maman|On va appeler un adulte.
-narrateur|Les prises sont pour les adultes. Les mains restent avec les jouets. Dahlia reprend une voiture rouge. Elle la fait rouler tout doux. Parce qu'elle a appelé, la lumière est là. Les mains tiennent les jouets. Dahlia est calme. Papa s'assoit près d'elle. Ils font un petit garage. Les mains restent avec les jouets.</t>
+          <t>narrateur|La poussière danse dans un rayon.
+narrateur|Le rayon est mince, tout pâle.
+narrateur|Des voitures en bois dorment par terre.
+narrateur|Le bois est lisse, un peu froid.
+narrateur|Une pile de livres attend près de la porte.
+narrateur|Papa range un livre, tout doux.
+narrateur|La pièce est un peu sombre.
+narrateur|Nino vit ici, avec papa et maman.
+enfant-m|Papa, la poussière danse !
+papa|Oui.
+papa|C'est le soleil.
+papa|Tu vois tes voitures ?
+enfant-m|Oui.
+enfant-m|Elles dorment.
+narrateur|En ce moment, Nino prend une voiture rouge.
+narrateur|Il la fait rouler tout doux.
+narrateur|Le bois fait un petit bruit.
+narrateur|Le rayon pâle ne suffit plus.
+enfant-m|Papa, la lumière.
+narrateur|Nino regarde ses mains.
+narrateur|Les mains avec les jouets.
+narrateur|Nino appelle papa.
+narrateur|On va appeler un adulte.
+papa|J'arrive, Nino.
+narrateur|Papa vient.
+narrateur|Papa allume.
+narrateur|La pièce devient claire.
+narrateur|Les voitures de bois brillent.
+maman|Tu as appelé un adulte ?
+enfant-m|Oui, maman.
+maman|Bravo, Nino.
+maman|On appelle papa ou maman pour la lumière.
+papa|Les prises sont pour les adultes.
+papa|Les mains avec les jouets.
+narrateur|Nino reprend la voiture rouge.
+narrateur|Il fait un petit garage.
+narrateur|Deux livres forment les murs.
+enfant-m|Le garage !
+papa|Oui.
+papa|Tu as fait du bon travail.
+narrateur|Parce qu'il a appelé, la lumière est là.
+narrateur|Les mains tiennent les jouets.
+papa|Tu ranges une voiture dans le garage ?
+enfant-m|Oui.
+narrateur|Papa s'assoit près de lui.
+narrateur|Le plancher est un peu froid.
+maman|Tes mains sont avec les jouets ?
+enfant-m|Oui, maman.
+maman|Bravo.
+narrateur|La poussière ne se voit plus.
+narrateur|La pièce est claire, tout simple.
+enfant-m|J'ai appelé un adulte.
+papa|Oui.
+papa|C'est bien.
+narrateur|Nino est calme.
+narrateur|La voiture rouge entre dans le garage.
+narrateur|Elle fait un petit toc.
+narrateur|Les autres voitures attendent leur tour.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>enfants_parc,voiture_passe</t>
+          <t>voitures_bois</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1413,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Dahlia veut la lumière. Que fait-elle ?</t>
+          <t>Nino veut la lumière. Que fait-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1508,7 +1573,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Dahlia veut la lumière. Que fait-elle ?</t>
+          <t>narrateur|Nino veut la lumière.
+narrateur|Que fait-il ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1536,7 +1602,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Dahlia a appelé un adulte. Les mains étaient avec les jouets. Papa et maman sont là.</t>
+          <t>Nino a appelé un adulte. Les mains avec les jouets. Tu as appelé un adulte ? Oui. Papa. Bravo, Nino. Tu as fait du bon travail. Les prises sont pour les adultes. La voiture rouge reste dans le garage. La lumière reste allumée.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1684,7 +1750,16 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Dahlia a appelé un adulte. Les mains étaient avec les jouets. Papa et maman sont là.</t>
+          <t>narrateur|Nino a appelé un adulte.
+narrateur|Les mains avec les jouets.
+papa|Tu as appelé un adulte ?
+enfant-m|Oui.
+enfant-m|Papa.
+maman|Bravo, Nino.
+maman|Tu as fait du bon travail.
+papa|Les prises sont pour les adultes.
+narrateur|La voiture rouge reste dans le garage.
+narrateur|La lumière reste allumée.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1712,7 +1787,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Dahlia pose la voiture dans le garage. La lumière reste allumée.</t>
+          <t>Nino pose une dernière voiture. Le garage est plein. Tu as fini ton garage ? Oui, papa. Bravo. La lumière reste allumée. Papa pose le dernier livre sur la pile. Tu as fini de ranger les livres ? Oui. Le plancher n'a plus de poussière visible. Les voitures de bois se reposent.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1852,7 +1927,17 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Dahlia pose la voiture dans le garage. La lumière reste allumée.</t>
+          <t>narrateur|Nino pose une dernière voiture.
+narrateur|Le garage est plein.
+papa|Tu as fini ton garage ?
+enfant-m|Oui, papa.
+papa|Bravo.
+maman|La lumière reste allumée.
+narrateur|Papa pose le dernier livre sur la pile.
+maman|Tu as fini de ranger les livres ?
+papa|Oui.
+narrateur|Le plancher n'a plus de poussière visible.
+narrateur|Les voitures de bois se reposent.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1880,7 +1965,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai appelé un adulte. Les mains avec les jouets. Bravo. C'est du bon travail. Le rayon de soleil s'en va, tout pâle. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2020,7 +2105,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai appelé un adulte.
+enfant-m|Les mains avec les jouets.
+papa|Bravo.
+maman|C'est du bon travail.
+narrateur|Le rayon de soleil s'en va, tout pâle.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2042,7 +2132,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2080,6 +2170,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.MAI.001-04.xlsx
+++ b/stories/arbres/ATOM-SEC.MAI.001-04.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>La poussière danse dans un rayon. Le rayon est mince, tout pâle. Des voitures en bois dorment par terre. Le bois est lisse, un peu froid. Une pile de livres attend près de la porte. Papa range un livre, tout doux. La pièce est un peu sombre. Nino vit ici, avec papa et maman. Papa, la poussière danse ! Oui. C'est le soleil. Tu vois tes voitures ? Oui. Elles dorment. En ce moment, Nino prend une voiture rouge. Il la fait rouler tout doux. Le bois fait un petit bruit. Le rayon pâle ne suffit plus. Papa, la lumière. Nino regarde ses mains. Les mains avec les jouets. Nino appelle papa. On va appeler un adulte. J'arrive, Nino. Papa vient. Papa allume. La pièce devient claire. Les voitures de bois brillent. Tu as appelé un adulte ? Oui, maman. Bravo, Nino. On appelle papa ou maman pour la lumière. Les prises sont pour les adultes. Les mains avec les jouets. Nino reprend la voiture rouge. Il fait un petit garage. Deux livres forment les murs. Le garage ! Oui. Tu as fait du bon travail. Parce qu'il a appelé, la lumière est là. Les mains tiennent les jouets. Tu ranges une voiture dans le garage ? Oui. Papa s'assoit près de lui. Le plancher est un peu froid. Tes mains sont avec les jouets ? Oui, maman. Bravo. La poussière ne se voit plus. La pièce est claire, tout simple. J'ai appelé un adulte. Oui. C'est bien. Nino est calme. La voiture rouge entre dans le garage. Elle fait un petit toc. Les autres voitures attendent leur tour.</t>
+          <t>La poussière danse dans un rayon. Le rayon est mince, tout pâle. Des voitures en bois dorment par terre. Le bois est lisse, un peu froid. Une pile de livres attend près de la porte. Papa range un livre, tout doux. La pièce est un peu sombre. Nino vit ici, avec papa et maman. Papa, la poussière danse ! Oui. C'est le soleil. Tu vois tes voitures ? Oui. Elles dorment. En ce moment, Nino prend une voiture rouge. Il la fait rouler tout doux. Le bois fait un petit bruit. Le rayon pâle ne suffit plus. Papa, la lumière. Nino regarde ses mains. Les mains avec les jouets. Nino appelle papa. On va appeler un adulte. J'arrive, Nino. Papa vient. Papa allume. La pièce devient claire. Les voitures de bois brillent. Tu as appelé un adulte ? Oui, maman. Bravo, Nino. On appelle papa ou maman pour la lumière. Les prises sont pour les adultes. Les mains avec les jouets. Nino reprend la voiture rouge. Il fait un petit garage. Deux livres forment les murs. Le garage ! Oui. Parce qu'il a appelé, la lumière est là. Les mains tiennent les jouets. Tu ranges une voiture dans le garage ? Oui. Papa s'assoit près de lui. Le plancher est un peu froid. Tes mains sont avec les jouets ? Oui, maman. Bravo. La poussière ne se voit plus. La pièce est claire, tout simple. J'ai appelé un adulte. Oui. C'est bien. Nino est calme. La voiture rouge entre dans le garage. Elle fait un petit toc. Les autres voitures attendent leur tour.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Dahlia joue dans la salle de jeux. Ses voitures en bois sont par terre. Papa range des livres près de la porte. La pièce est un peu sombre. Dahlia veut plus de lumière. Elle regarde ses mains. Les mains restent avec les jouets. Dahlia appelle un adulte. Elle dit : papa, la lumière. Papa vient. Papa allume. La pièce devient claire. Maman entre. Maman dit : on va &lt;emphasis level="moderate"&gt;appeler&lt;/emphasis&gt; un adulte. Les prises sont pour les adultes. Les mains restent avec les jouets. Dahlia reprend une voiture rouge. Elle la fait rouler tout doux. Parce qu'elle a appelé, la lumière est là. Les mains tiennent les jouets. Dahlia est calme. Papa s'assoit près d'elle. Ils font un petit garage. Les mains restent avec les jouets.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>La poussière danse dans un rayon. Le rayon est mince, tout pâle. Des voitures en bois dorment par terre. Le bois est lisse, un peu froid. Une pile de livres attend près de la porte. Papa range un livre, tout doux. La pièce est un peu sombre. Nino vit ici, avec papa et maman. Papa, la poussière danse ! Oui. C'est le soleil. Tu vois tes voitures ? Oui. Elles dorment. En ce moment, Nino prend une voiture rouge. Il la fait rouler tout doux. Le bois fait un petit bruit. Le rayon pâle ne suffit plus. Papa, la lumière. Nino regarde ses mains. Les mains avec les jouets. Nino appelle papa. On va appeler un adulte. J'arrive, Nino. Papa vient. Papa allume. La pièce devient claire. Les voitures de bois brillent. Tu as appelé un adulte ? Oui, maman. Bravo, Nino. On appelle papa ou maman pour la lumière. Les prises sont pour les adultes. Les mains avec les jouets. Nino reprend la voiture rouge. Il fait un petit garage. Deux livres forment les murs. Le garage ! Oui. Parce qu'il a appelé, la lumière est là. Les mains tiennent les jouets. Tu ranges une voiture dans le garage ? Oui. Papa s'assoit près de lui. Le plancher est un peu froid. Tes mains sont avec les jouets ? Oui, maman. Bravo. La poussière ne se voit plus. La pièce est claire, tout simple. J'ai appelé un adulte. Oui. C'est bien. Nino est calme. La voiture rouge entre dans le garage. Elle fait un petit toc. Les autres voitures attendent leur tour.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1363,7 +1363,6 @@
 narrateur|Deux livres forment les murs.
 enfant-m|Le garage !
 papa|Oui.
-papa|Tu as fait du bon travail.
 narrateur|Parce qu'il a appelé, la lumière est là.
 narrateur|Les mains tiennent les jouets.
 papa|Tu ranges une voiture dans le garage ?
@@ -1418,7 +1417,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Dahlia veut la lumière. Que fait-elle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nino veut la lumière. Que fait-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1577,7 +1576,6 @@
 narrateur|Que fait-il ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1602,12 +1600,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Nino a appelé un adulte. Les mains avec les jouets. Tu as appelé un adulte ? Oui. Papa. Bravo, Nino. Tu as fait du bon travail. Les prises sont pour les adultes. La voiture rouge reste dans le garage. La lumière reste allumée.</t>
+          <t>Nino a appelé un adulte. Les mains avec les jouets. Tu as appelé un adulte ? Oui. Papa. Bravo, Nino. Les prises sont pour les adultes. La voiture rouge reste dans le garage. La lumière reste allumée.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Dahlia a appelé un adulte. Les &lt;emphasis level="moderate"&gt;mains&lt;/emphasis&gt; étaient avec les jouets. Papa et maman sont là.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nino a appelé un adulte. Les mains avec les jouets. Tu as appelé un adulte ? Oui. Papa. Bravo, Nino. Les prises sont pour les adultes. La voiture rouge reste dans le garage. La lumière reste allumée.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1756,13 +1754,11 @@
 enfant-m|Oui.
 enfant-m|Papa.
 maman|Bravo, Nino.
-maman|Tu as fait du bon travail.
 papa|Les prises sont pour les adultes.
 narrateur|La voiture rouge reste dans le garage.
 narrateur|La lumière reste allumée.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1792,7 +1788,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Dahlia pose la voiture dans le garage. La lumière reste allumée.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nino pose une dernière voiture. Le garage est plein. Tu as fini ton garage ? Oui, papa. Bravo. La lumière reste allumée. Papa pose le dernier livre sur la pile. Tu as fini de ranger les livres ? Oui. Le plancher n'a plus de poussière visible. Les voitures de bois se reposent.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1940,7 +1936,6 @@
 narrateur|Les voitures de bois se reposent.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1965,12 +1960,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai appelé un adulte. Les mains avec les jouets. Bravo. C'est du bon travail. Le rayon de soleil s'en va, tout pâle. L'histoire est finie.</t>
+          <t>J'ai appelé un adulte. Les mains avec les jouets. Bravo. Le rayon de soleil s'en va, tout pâle.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai appelé un adulte. Les mains avec les jouets. Bravo. Le rayon de soleil s'en va, tout pâle.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2108,12 +2103,9 @@
           <t>enfant-m|J'ai appelé un adulte.
 enfant-m|Les mains avec les jouets.
 papa|Bravo.
-maman|C'est du bon travail.
-narrateur|Le rayon de soleil s'en va, tout pâle.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|Le rayon de soleil s'en va, tout pâle.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2132,7 +2124,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2177,6 +2169,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.MAI.001-04.xlsx
+++ b/stories/arbres/ATOM-SEC.MAI.001-04.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>salle de jeux</t>
+          <t>salle de jeux, voitures en bois, pile de livres</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Dahlia, papa, maman</t>
+          <t>Nino, papa, maman</t>
         </is>
       </c>
     </row>
